--- a/зыуз.xlsx
+++ b/зыуз.xlsx
@@ -89,7 +89,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -236,12 +236,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -249,19 +249,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -270,6 +264,22 @@
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Денежный" xfId="1" builtinId="4"/>
@@ -555,12 +565,12 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="12" width="9" bestFit="1" customWidth="1"/>
@@ -586,7 +596,7 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="19" t="s">
         <v>11</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -604,28 +614,28 @@
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="24">
         <v>50000</v>
       </c>
       <c r="C2" s="1">
         <v>20</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="15">
         <f>B2*C2/100</f>
         <v>10000</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="15">
         <f>(B2+D2)*0.13</f>
         <v>7800</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="15">
         <f>B2+D2-E2</f>
         <v>52200</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="20">
         <v>1</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="6">
         <v>0.15</v>
       </c>
       <c r="I2" s="5">
@@ -652,25 +662,25 @@
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="24">
         <v>45000</v>
       </c>
       <c r="C3" s="1">
         <v>15</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="15">
         <f t="shared" ref="D3:D6" si="1">B3*C3/100</f>
         <v>6750</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="15">
         <f t="shared" ref="E3:E6" si="2">(B3+D3)*0.13</f>
         <v>6727.5</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="15">
         <f t="shared" ref="F3:F6" si="3">B3+D3-E3</f>
         <v>45022.5</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="20">
         <v>2</v>
       </c>
       <c r="H3" s="5"/>
@@ -687,25 +697,25 @@
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="24">
         <v>62000</v>
       </c>
       <c r="C4" s="1">
         <v>25</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="15">
         <f t="shared" si="1"/>
         <v>15500</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="15">
         <f t="shared" si="2"/>
         <v>10075</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="15">
         <f t="shared" si="3"/>
         <v>67425</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="20">
         <v>3</v>
       </c>
       <c r="H4" s="5"/>
@@ -722,25 +732,25 @@
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="24">
         <v>55000</v>
       </c>
       <c r="C5" s="1">
         <v>10</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="15">
         <f t="shared" si="1"/>
         <v>5500</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="15">
         <f t="shared" si="2"/>
         <v>7865</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="15">
         <f t="shared" si="3"/>
         <v>52635</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="20">
         <v>4</v>
       </c>
       <c r="H5" s="5"/>
@@ -757,25 +767,25 @@
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="24">
         <v>40000</v>
       </c>
       <c r="C6" s="1">
         <v>30</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="15">
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="15">
         <f t="shared" si="2"/>
         <v>6760</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="15">
         <f t="shared" si="3"/>
         <v>45240</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="20">
         <v>5</v>
       </c>
       <c r="H6" s="5"/>
@@ -789,129 +799,129 @@
       <c r="M6" s="5"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="16">
         <f>SUM(B2:B6)</f>
         <v>252000</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17">
-        <f t="shared" ref="C7:F7" si="5">SUM(D2:D6)</f>
+      <c r="C7" s="13"/>
+      <c r="D7" s="16">
+        <f t="shared" ref="D7:F7" si="5">SUM(D2:D6)</f>
         <v>49750</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="16">
         <f t="shared" si="5"/>
         <v>39227.5</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="16">
         <f t="shared" si="5"/>
         <v>262522.5</v>
       </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="17">
         <f>AVERAGE(F2:F6)</f>
         <v>52504.5</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="26">
         <f>MAX(F2:F6)</f>
         <v>67425</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="17">
         <f>MIN(F2:F6)</f>
         <v>45022.5</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
     </row>
     <row r="100" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="18" t="s">
         <v>18</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
       </c>
-      <c r="D100" t="s">
-        <v>18</v>
-      </c>
-      <c r="E100" t="s">
-        <v>18</v>
-      </c>
-      <c r="F100" t="s">
-        <v>18</v>
-      </c>
-      <c r="G100" t="s">
+      <c r="D100" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E100" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F100" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" s="23" t="s">
         <v>18</v>
       </c>
       <c r="H100" t="s">

--- a/зыуз.xlsx
+++ b/зыуз.xlsx
@@ -91,7 +91,7 @@
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,8 +143,32 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,6 +184,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -236,17 +266,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -268,9 +291,6 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -280,6 +300,20 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Денежный" xfId="1" builtinId="4"/>
@@ -565,95 +599,95 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.33203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="20">
         <v>50000</v>
       </c>
       <c r="C2" s="1">
         <v>20</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="12">
         <f>B2*C2/100</f>
         <v>10000</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="12">
         <f>(B2+D2)*0.13</f>
         <v>7800</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="12">
         <f>B2+D2-E2</f>
         <v>52200</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="16">
         <v>1</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="3">
         <v>0.15</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="2">
         <v>1.5</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="2">
         <f>B2*$I$2</f>
         <v>75000</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="2">
         <f>B2*I$2</f>
         <v>75000</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="2">
         <f t="shared" ref="L2:M2" si="0">C2*J$2</f>
         <v>1500000</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="2">
         <f t="shared" si="0"/>
         <v>750000000</v>
       </c>
@@ -662,266 +696,266 @@
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="20">
         <v>45000</v>
       </c>
       <c r="C3" s="1">
         <v>15</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="12">
         <f t="shared" ref="D3:D6" si="1">B3*C3/100</f>
         <v>6750</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="12">
         <f t="shared" ref="E3:E6" si="2">(B3+D3)*0.13</f>
         <v>6727.5</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="12">
         <f t="shared" ref="F3:F6" si="3">B3+D3-E3</f>
         <v>45022.5</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="16">
         <v>2</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5">
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2">
         <f t="shared" ref="J3:J6" si="4">B3*$I$2</f>
         <v>67500</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="20">
         <v>62000</v>
       </c>
       <c r="C4" s="1">
         <v>25</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="12">
         <f t="shared" si="1"/>
         <v>15500</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="12">
         <f t="shared" si="2"/>
         <v>10075</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="12">
         <f t="shared" si="3"/>
         <v>67425</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="16">
         <v>3</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5">
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2">
         <f t="shared" si="4"/>
         <v>93000</v>
       </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="20">
         <v>55000</v>
       </c>
       <c r="C5" s="1">
         <v>10</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="12">
         <f t="shared" si="1"/>
         <v>5500</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="12">
         <f t="shared" si="2"/>
         <v>7865</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="12">
         <f t="shared" si="3"/>
         <v>52635</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="16">
         <v>4</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5">
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2">
         <f t="shared" si="4"/>
         <v>82500</v>
       </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="20">
         <v>40000</v>
       </c>
       <c r="C6" s="1">
         <v>30</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="12">
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="12">
         <f t="shared" si="2"/>
         <v>6760</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="12">
         <f t="shared" si="3"/>
         <v>45240</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="16">
         <v>5</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2">
         <f t="shared" si="4"/>
         <v>60000</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="13">
         <f>SUM(B2:B6)</f>
         <v>252000</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="16">
+      <c r="C7" s="10"/>
+      <c r="D7" s="13">
         <f t="shared" ref="D7:F7" si="5">SUM(D2:D6)</f>
         <v>49750</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="13">
         <f t="shared" si="5"/>
         <v>39227.5</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="13">
         <f t="shared" si="5"/>
         <v>262522.5</v>
       </c>
-      <c r="G7" s="21"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="14">
         <f>AVERAGE(F2:F6)</f>
         <v>52504.5</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="22">
         <f>MAX(F2:F6)</f>
         <v>67425</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="14">
         <f>MIN(F2:F6)</f>
         <v>45022.5</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
     </row>
     <row r="100" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
-      <c r="B100" s="18" t="s">
+      <c r="B100" s="15" t="s">
         <v>18</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
       </c>
-      <c r="D100" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E100" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="F100" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="G100" s="23" t="s">
+      <c r="D100" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F100" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" s="19" t="s">
         <v>18</v>
       </c>
       <c r="H100" t="s">
